--- a/text/foundationScores/milkywayvodka_6_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/milkywayvodka_6_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG40"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,104 +604,114 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>32.984</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>21.192</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>72.2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>6.2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>21.6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>71.84</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">  She took a deep breath and tried to calm down.  The situation seemed too good, and after she spent most of the last week's worrying, she knew she could enjoy the moment.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.02621096239643085</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>0.02967599178125494</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.04572951541148482</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.03093741275559457</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.02560228377972301</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.08233163157556983</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0720437327678117</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.05180971551261407</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.06087111530639312</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.05679510623746696</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>2.25</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>0.0617136224543632</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>0.03564593301435406</v>
       </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>0.04938198248525258</v>
       </c>
-      <c r="V2" t="n">
+      <c r="X2" t="n">
         <v>0.03057823841429369</v>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>0.08810888422097185</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.05476539467709446</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>0.04192424221688448</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AB2" t="n">
         <v>0.06859680567076108</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.1376674846075603</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>0.0928335395333737</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AE2" t="n">
         <v>0.09462732675768783</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AF2" t="n">
         <v>0.02566721132897604</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AG2" t="n">
         <v>0.04301110194016467</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="n">
         <v>0.04680030681263325</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>2.25</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>46.677</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>34.285</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>74.7</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>7.199999999999999</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>18.1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>58.59</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">  She looked at her reflection in the mirror and started laughing uncontrollably.  That evening, at her biggest moment of triumph, she did the expected, calling her mother to brag.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.01440329218106996</v>
       </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.04366084735438303</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.009578544061302681</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.01215277777777778</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.09437576605686364</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.05650127674921473</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.04474313022700119</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.07009422477411072</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.06579082019405701</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.75</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
         <v>0.024</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.04483695652173913</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0.002985074626865672</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.02434567901234568</v>
       </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0.1348913565856608</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.1027572187572188</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.07761744428411095</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>0.1128685236984466</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>0.1085446434766283</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>0.1396442716471059</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>0.11114076636623</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>0.5555555555555556</v>
       </c>
     </row>
@@ -804,104 +834,114 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>64.638</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>48.108</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>79.10000000000001</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>20.9</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>84.39</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve"> In general, conversations with her mother resembled an intense and unbelievably optimistic lecture about all the good things she had accomplished in her life, starting from how she managed to slide from her mother's womb up to the way she had reached the finals in American Idol.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.01845872684782819</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.01186757215619695</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.04207808901354725</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.0243364072822835</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.02537568099109601</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0950238218354264</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.06462573677697044</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.03910538347996902</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.0277310039258831</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.0425691818650799</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>1.2</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.05361907569829085</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.09086364100550888</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.04081041369176962</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.07344504314784933</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.09726792438315338</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.08046058949574013</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>0.01539400515394005</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>0.08029036982289016</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>0.06252078723988837</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>0.06857216857216858</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>0.06152032894833291</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>0.05613149952772594</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>0.1227698571978813</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.04904439052490812</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.6923076923076923</v>
       </c>
     </row>
@@ -909,104 +949,114 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>73.007</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>66.622</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>65.90000000000001</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>34.1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>83.16</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">  To be honest, it wasn't far from the truth.  Her mother had gone through only two hours of relaxed labor.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.03520220588235294</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.07041063530610568</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.05474198719493195</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.04835475719622061</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.04803045349222112</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.06363306992795961</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.04690837745392556</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.05034188034188034</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0.02851640744668316</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>0.03444905788655788</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>3</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>0.0958100558659218</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>0.04462279293739968</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>0.07538239538239538</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.08700066558436978</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>0.04017857142857143</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>0.1938577464514496</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.09335550935550936</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.06275946275946276</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>0.0805997273966379</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>0.05816070721731099</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.06063492063492063</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -1014,104 +1064,114 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>86.824</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>73.548</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>68.30000000000001</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>4.100000000000001</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>27.6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>91.36</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">  She could imagine, though she never actually tried, it could have gone worse.  But to this day, every time she looked at her mom's belly, she felt that it was a safe haven that truly felt nice and warm.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.05593264810538764</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.04951475223363049</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.05029065930236692</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.04027478030984752</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.0376012876012876</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.05408428414812017</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.02719491798692922</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0525110799460512</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.01958901179367374</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.05381044353082095</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>4.333333333333333</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>0.1200745623920066</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.1004124341209317</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>0.0623865245831792</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>0.05373171445661765</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>0.1138116633093769</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.09902175121349638</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>0.06172101920492479</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>0.08788983632730268</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.0576569415327277</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.05551541689472724</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>0.07602446129473328</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>0.07784592280080385</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>0.03065134099616858</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.0435174573211383</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>1.285714285714286</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>106.084</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>88.946</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>77.8</v>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
         <v>22.2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>91.86</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">  As for Idle, it wasn't that simple, as nothing in life ever is.  She did pick a great song, and well, she did take it for granted, although it was better than anything she could ever hope for, and she could go on and on and on about all the things that worked out.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.03462014845868015</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.06528450167833172</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.065232486865464</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.05830269311809792</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.05497769852561654</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.0644364998108366</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.05002475869942084</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0245400205473055</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.04544732196934078</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.03119659837796353</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>2.666666666666667</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.0666799668747987</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.1477516163621652</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.06932395926303711</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.07820725396547543</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.1361687057081215</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.09023248231876077</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.07014286019119154</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.05731531607243071</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.02016129032258064</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.05854700854700855</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.06900683578315157</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.02541208791208791</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.04226190476190476</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.02341732126214885</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>2.666666666666667</v>
       </c>
     </row>
@@ -1224,104 +1294,114 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>117.062</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>107.025</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>82.39999999999999</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>17.6</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>-81.26000000000001</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">  But it was beside the point.  She learned her lesson, or so she told everyone, not understanding what the lesson was and how the hell was she supposed to learn it.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.04285714285714286</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.0216998191681736</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.0376658753527938</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.03463885861627846</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0198565128142593</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.06013851205277966</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.06135867241220187</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.03580279239251689</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.0270251286996676</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.06696735700031289</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>3.5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.08513210108604845</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.1338077866805637</v>
       </c>
-      <c r="U8" t="n">
+      <c r="W8" t="n">
         <v>0.0852935137766984</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>0.02941176470588236</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>0.1052345807146015</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>0.07480192416525185</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.05302033151054833</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>0.03933963288801998</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.01908396946564886</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.09121982209385306</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.03944444444444444</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.0515878897672376</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.03950617283950617</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>124.8</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>118.51</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>55.60000000000001</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>44.4</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>90.41</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> Her mom recognized her elated mood and said to her enthusiastically, I'm so proud of you, Rachel.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.06539036544850499</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.03515379786566227</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.0666668385947629</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.02545454545454545</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>0.02978723404255319</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.008844439089046873</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.009457769694213938</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.02670525010334849</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.0549303683737646</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.08291128888288041</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>0.0625</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>0.2631578947368421</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>0.06</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>0.1388888888888889</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>0.09375</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.03542234332425068</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>0.03963221306277743</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>0.04338771259979174</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.03931080628972901</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>0.0333696046427276</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>0.02737752161383285</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>0.01955888472742405</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>131.891</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>124.86</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>79.5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>20.5</v>
       </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>-65.97</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve">  Listen to me.  This might sound a bit obnoxious, but have you forgone the idea of seeing a psychic about your stage fright?</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.07410833225439846</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.06438865496783146</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.03900044447930556</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.05568253968253969</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>0.02944359562006621</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>0.0301357257878997</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.01639344262295082</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.01794871794871795</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.0303109713487072</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.05780652480193219</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>1.5</v>
       </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
         <v>0.07602684808704528</v>
       </c>
-      <c r="T10" t="n">
+      <c r="V10" t="n">
         <v>0.1953208556149733</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.08342767295597484</v>
       </c>
-      <c r="V10" t="n">
+      <c r="X10" t="n">
         <v>0.1083465959328028</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
         <v>0.04942716857610475</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>0.04027531688701104</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.06398046398046398</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
       <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
         <v>0.0722943722943723</v>
       </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
         <v>0.008695652173913044</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.02105263157894737</v>
       </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>140.124</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>133.333</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>72.2</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>27.8</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>69.67999999999999</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve">  Wow, mom, that was just a fleeting idea.  I'm not that desperate.  Bambi, I know you aren't.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.03609913793103448</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.0253280186015612</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0390304474589291</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.01223491027732463</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>0.01737967914438503</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>0.02654338685015291</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.03469995419147962</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.03435534591194969</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.07383068479685452</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.1354337152209493</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.07352941176470588</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.04528985507246377</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.07471264367816093</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.03846153846153846</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.05371900826446281</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>0.03296703296703297</v>
       </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
         <v>0.07228915662650602</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>0.09740259740259741</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>0.05454545454545454</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.0546875</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.03316326530612245</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>154.272</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>141.526</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>73.5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>19.9</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>6.600000000000001</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>-71.84</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">  She sometimes hated her mom for her random comments, but she had a point.  Sure, Mom, I'm done with that, she said hesitantly as she hung up and thought to herself, what do I have to lose?</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.03138586956521739</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.02014019814424605</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.05254459879295249</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.01102941176470588</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.006720430107526882</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.04216269642532418</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.04345609498468659</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.03507532956685499</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.05299558326712068</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.07923918074500763</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>2</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.05311546192213207</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.02430555555555556</v>
       </c>
-      <c r="U12" t="n">
+      <c r="W12" t="n">
         <v>0.05238095238095238</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.05673624288425047</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.05380730380730381</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>0.02688172043010753</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.03746823480470623</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.1179989504070725</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>0.1314999645697125</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>0.09064379345279457</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.07098059546495303</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.1032063502700689</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.07973745637181839</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.0541386758615223</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1749,73 +1869,77 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>163.873</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>156.617</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>73.5</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>26.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>75.79000000000001</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve"> She woke up late the next morning and calmly scanned the newspaper for the combination of best and nearest psychic.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.008375209380234507</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.03100775193798449</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>0.0425531914893617</v>
       </c>
-      <c r="L13" t="n">
+      <c r="N13" t="n">
         <v>0.03053847905282331</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.01265822784810127</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.02166643551692786</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.04374967378255649</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.02173823115744188</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.08247422680412371</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>0.09259259259259259</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
@@ -1823,30 +1947,36 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
       <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
         <v>0.05833333333333333</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AE13" t="n">
         <v>0.07920792079207921</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.06976744186046512</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.1411764705882353</v>
       </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>170.529</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>164.123</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>77.2</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>5.7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>17.1</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>58.59</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve"> Before long, she understood that, knowing nothing about the subject, it was hard to figure out which psychic was the best.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.02811584403876493</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.05964213754137709</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.0483124908585637</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
         <v>0.02439024390243902</v>
       </c>
-      <c r="L14" t="n">
+      <c r="N14" t="n">
         <v>0.01709401709401709</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.06154616017184733</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.04640023315282791</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.05500509911868526</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.07987952217279405</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.06390556255718637</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.1047248803827751</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.08732558139534885</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.1087914023960536</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.1090025457070123</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.05965532479010163</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.02649006622516556</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.09166022419791264</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.1615316316118627</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.09785289424053387</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>0.06419457735247208</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AF14" t="n">
         <v>0.1035137701804368</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AG14" t="n">
         <v>0.03246753246753246</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AH14" t="n">
         <v>0.0297661233167966</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1959,88 +2099,92 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>179.338</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>171.27</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>83.7</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>16.3</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>62.49</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve">  She would have to settle for the nearest one she could find.  Hermione the Great, pedicurist and fortune teller, money back guaranteed.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.03115264797507788</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.02815315315315315</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.06713352007469654</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
         <v>0.05473986047529063</v>
       </c>
-      <c r="L15" t="n">
+      <c r="N15" t="n">
         <v>0.02205882352941177</v>
       </c>
-      <c r="M15" t="n">
+      <c r="O15" t="n">
         <v>0.05803500397772474</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.1647566357109926</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.01626016260162602</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.08476190476190476</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>0.5</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.2105319913731128</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>0.1785048151954627</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>0.1468637992831541</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.08431050149279565</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.1940476190476191</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>0.1499157776530039</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>0.02873563218390805</v>
       </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
@@ -2054,9 +2198,15 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
         <v>0.188953488372093</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -2064,104 +2214,114 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>188.587</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>179.398</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>79.40000000000001</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>20.6</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>75.73999999999999</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve"> The combination was kind of intriguing, and just the thought of Harry Potter, which was her all-time favorite book by far, made the choice even more exciting.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.01684636118598383</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.07477922265559374</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.07272257111768321</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.06625708994743494</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.0370245316908905</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.0459062289042944</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.02798383048028201</v>
       </c>
-      <c r="O16" t="n">
+      <c r="Q16" t="n">
         <v>0.02118561710398445</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>0.02596202551075227</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.02811891800351968</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>1.4</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.03820879703232644</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.101873787331572</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.04652272894176398</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.08202597734056838</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.09778049562102718</v>
       </c>
-      <c r="X16" t="n">
+      <c r="Z16" t="n">
         <v>0.09697883281550207</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AA16" t="n">
         <v>0.03152709359605912</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AB16" t="n">
         <v>0.1210478039953713</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AC16" t="n">
         <v>0.0634954193093728</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AD16" t="n">
         <v>0.0962175092730297</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AE16" t="n">
         <v>0.02787427626137304</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AF16" t="n">
         <v>0.07056197990518065</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AG16" t="n">
         <v>0.02985074626865672</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AH16" t="n">
         <v>0.04687265601903771</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AI16" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2169,104 +2329,114 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>196.623</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>189.908</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>62.8</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>13</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>24.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>40.19</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">  A sweet voice answered her call.  It's your lucky day, Ms. Monroe.  Somehow a fake name felt sexier.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.02857142857142857</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.02022058823529412</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.03296703296703296</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.02058823529411765</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.05901794724636073</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.1026974774184227</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.05727896341463415</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.06699502954065283</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.07334575453535772</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.1145833333333333</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0759493670886076</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.1099093140615632</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0.03608145512060103</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Z17" t="n">
         <v>0.06251526251526252</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AA17" t="n">
         <v>0.01024422644594318</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>0.1531016731016731</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AC17" t="n">
         <v>0.06788793103448276</v>
       </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
         <v>0.1281377262235552</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>0.09433962264150943</v>
       </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
         <v>0.06172839506172839</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -2274,104 +2444,114 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>213.608</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>197.284</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>62.7</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>2.5</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>34.8</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>96.61999999999999</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">  I have a place at 5.30 p.m. today, but it's going to be rainy, so be sure to bring an umbrella.  She arrived at Hermione's clinic at 5.36, and Hermione, who to her delight was a surprisingly beautiful magician, welcomed her in.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.1049140265032319</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>0.04096337054353617</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.08739875535541171</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.05406581391236122</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>0.06652486631324857</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>0.04961073890011602</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.02972647141004139</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.03210308622335349</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.03001075340165602</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.03020683535783129</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.7</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.09096453123573227</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>0.1189276485788114</v>
       </c>
-      <c r="U18" t="n">
+      <c r="W18" t="n">
         <v>0.07238095238095238</v>
       </c>
-      <c r="V18" t="n">
+      <c r="X18" t="n">
         <v>0.05491551459293394</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Y18" t="n">
         <v>0.1660583882234474</v>
       </c>
-      <c r="X18" t="n">
+      <c r="Z18" t="n">
         <v>0.108089400667204</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AA18" t="n">
         <v>0.0462253193960511</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AB18" t="n">
         <v>0.07717561647974019</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AC18" t="n">
         <v>0.1069873845060412</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AD18" t="n">
         <v>0.06386513978354696</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
         <v>0.09688304945314291</v>
       </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
       <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
         <v>0.05012398976103657</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AI18" t="n">
         <v>0.5454545454545454</v>
       </c>
     </row>
@@ -2379,104 +2559,114 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>221.925</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>214.509</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>66.90000000000001</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>33.1</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>83.59999999999999</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">  I love Tuesdays, she said.  For some reason, everyone seems to be happy.  I know what you mean.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.05201863354037267</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.0320292389201462</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.08801710311718959</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.04205067172387549</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.04025327905924921</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.03809891899504397</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.02943262986068983</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.01846863472799758</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.03009683723129978</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>6</v>
       </c>
-      <c r="S19" t="n">
+      <c r="U19" t="n">
         <v>0.114482749902024</v>
       </c>
-      <c r="T19" t="n">
+      <c r="V19" t="n">
         <v>0.06851115096551202</v>
       </c>
-      <c r="U19" t="n">
+      <c r="W19" t="n">
         <v>0.09534654284610899</v>
       </c>
-      <c r="V19" t="n">
+      <c r="X19" t="n">
         <v>0.04853867883528901</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Y19" t="n">
         <v>0.07556497175141243</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>0.138325131995672</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AA19" t="n">
         <v>0.03760933548895245</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AB19" t="n">
         <v>0.02912346509076755</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.03730712322976115</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.01446257086659725</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.0387481068455587</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AF19" t="n">
         <v>0.08395006936366782</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AG19" t="n">
         <v>0.009125840537944284</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AH19" t="n">
         <v>0.03777607021320237</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>233.202</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>222.426</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>81.2</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>18.8</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>69.08</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">  I used to be in the phone book industry, Rachel replied, feeling that was a satisfactory response.  So, are you interested in pedicure session, or are you just here for fortune telling?</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.05649963070112512</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.0358363221693742</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.03989105523632377</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.05727222696936002</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.04502705627705628</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.07294763843480764</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.03510858633809454</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.0538961038961039</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.006193693693693694</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.04328096809906511</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>1.6</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.08681422063775006</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
         <v>0.0196078431372549</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.06785496773331268</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0.072551495345613</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>0.04069609967497292</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>0.04475308641975308</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>0.08234519104084322</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.1549146420856947</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.0544468506487497</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>0.1034094066046313</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>0.08997948946054808</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AG20" t="n">
         <v>0.0499113475177305</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AH20" t="n">
         <v>0.05319828626280238</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.8571428571428571</v>
       </c>
     </row>
@@ -2589,104 +2789,114 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>240.473</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>233.622</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>74.7</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>25.3</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>72.69</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve">  Hermione asked.  Just the fortune telling.  My toenails seem to be just glowing these days, thank you, Rachel said proudly.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.04434046345811051</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.05128960905699355</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.04294012706786256</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.07124811463046758</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.025206492257535</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.01182221211776742</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.05433448408131952</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.01137129380053908</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.03893241612376964</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>0.09529211571185479</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.02531645569620253</v>
       </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
         <v>0.07593457943925234</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>0.009259259259259259</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>0.07822883151936862</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>0.1486270766383778</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AD21" t="n">
         <v>0.02892514173319449</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AE21" t="n">
         <v>0.05745720419315267</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>0.1222464030951517</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AG21" t="n">
         <v>0.01825168107588857</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AH21" t="n">
         <v>0.03355207699776988</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>0.375</v>
       </c>
     </row>
@@ -2694,88 +2904,92 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>248.164</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>241.274</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>48.1</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>12.5</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>39.4</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>68.08</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Sure, darling, Hermione replied and grinned.  What seems to be bothering you, Ms. Monroe?</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.06304347826086956</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.05708661417322835</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.06127450980392156</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.06197478991596639</v>
       </c>
-      <c r="L22" t="n">
+      <c r="N22" t="n">
         <v>0.06854838709677419</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.01388888888888889</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.03030303030303031</v>
       </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.1683168316831683</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.2142857142857143</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.2580645161290323</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.1612903225806452</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.04878048780487805</v>
       </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
@@ -2792,6 +3006,12 @@
         <v>0</v>
       </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
         <v>0.1428571428571428</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>258.555</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>249.022</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>81.5</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>14</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>4.5</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>-61.31</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  It's Simon, the meanest judge in American Idol.  I can't stop thinking about him.  I am supposed to participate in the final, but I am afraid to panic.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.01724137931034483</v>
       </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.03460880205066252</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.009966777408637875</v>
       </c>
-      <c r="L23" t="n">
+      <c r="N23" t="n">
         <v>0.003861003861003862</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.07795552061581519</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.1009554464213661</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.06475790140710451</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>0.09014400409942892</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0900455891030658</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>1.4</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>0.009920634920634922</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>0.04846589798710182</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>0.09277701465201464</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.006912442396313364</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>0.04360902255639098</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.04933542764652883</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.002380952380952381</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.1405017921146953</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.1217574762402348</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.09876204324687914</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.1885631575243623</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AF23" t="n">
         <v>0.0919506264044079</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AG23" t="n">
         <v>0.02538556793875943</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AH23" t="n">
         <v>0.1188633671779739</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>1.4</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>266.887</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>259.477</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>0.18</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  I'm absolutely obsessed with him.  I dream about him constantly, and I imagine his voice in almost every man I hear.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.03945037796647954</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.04728008715006739</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.06614362788363314</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.03300229182582124</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.03767747236115716</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.05451879789818231</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.06821039536497499</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.02476197524859776</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.086037882876131</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.07540843390074396</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>7</v>
       </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
       <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
         <v>0.09632034632034632</v>
       </c>
-      <c r="V24" t="n">
+      <c r="X24" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Y24" t="n">
         <v>0.0375</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.07509157509157507</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AA24" t="n">
         <v>0.02631578947368421</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AB24" t="n">
         <v>0.1914144736842105</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.2260007350975675</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AD24" t="n">
         <v>0.05772151898734177</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AE24" t="n">
         <v>0.09415323632191101</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AF24" t="n">
         <v>0.0879416282642089</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AG24" t="n">
         <v>0.03205128205128205</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AH24" t="n">
         <v>0.08279264666125979</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>274.658</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>266.927</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>72.09999999999999</v>
       </c>
-      <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>27.9</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>70.03</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">  To be honest, you are the first person I've confided with.  Do you like vodka, Ms. Monroe?</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.05013314536340852</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.06386427861281302</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.04462747112780829</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.03468639018520149</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.02291650752425331</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.05510752688172043</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.04693140794223827</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.03516819571865444</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.01801801801801802</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.04603174603174603</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.75</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.09383570421632706</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.1242427203439515</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.009259259259259259</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.004942339373970346</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.1155604246156171</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.05984251968503937</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.006038647342995169</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
       <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
         <v>0.07851239669421488</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AE25" t="n">
         <v>0.05327868852459016</v>
       </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
       <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -3114,104 +3364,114 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>283.127</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>275.853</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>90.40000000000001</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>9.6</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>37.24</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve"> Rachel didn't understand the relevance of the question, but she replied nevertheless, I'm not crazy about it, but I drink a sip now and then.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.02014388489208633</v>
       </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>0.04488447696294991</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.06837219722975067</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.04416189870735325</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.09101542364144441</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.1014825053795266</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0298989898989899</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.006896551724137929</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>0.06370967741935483</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.04123711340206185</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0380952380952381</v>
       </c>
-      <c r="U26" t="n">
+      <c r="W26" t="n">
         <v>0.04245283018867924</v>
       </c>
-      <c r="V26" t="n">
+      <c r="X26" t="n">
         <v>0.03816793893129771</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Y26" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.0352112676056338</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.05833333333333333</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AE26" t="n">
         <v>0.06451612903225806</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AF26" t="n">
         <v>0.04950495049504951</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AG26" t="n">
         <v>0.06452581032412966</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.05681818181818182</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>292.384</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>283.187</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>89.3</v>
       </c>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>10.7</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>45.88</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve"> Just keep your eyes on the vodka bottle, Hermione said, as she started to gently caress a tiny vodka bottle which was standing on the table.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.007575757575757576</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>0.02806231327358088</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.03799363023797947</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.02901329243353783</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.04323671497584541</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.06860685737822426</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.05038153049026714</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.05033851055356432</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>0.06957454799790098</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.02798180046927118</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.05</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.1345882352941176</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
         <v>0.01923076923076923</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.02962962962962963</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>0.04379310344827586</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AB27" t="n">
         <v>0.179199142383729</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AC27" t="n">
         <v>0.01585288522511097</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.08710817145966979</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.1612171750868325</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.1086574597754046</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>0.1022752095587752</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.05601033978267354</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.625</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>302.529</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>293.566</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>74.2</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>7.8</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>18</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>44.04</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve">  Aren't you supposed to do that with a crystal ball?  Rachel asked doubtfully.  Put your trust in Hermione and everything will be just fine."</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.08797814207650273</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.0573351452792338</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.08098290598290599</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.09092451229855809</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0.0471976401179941</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0219409282700422</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.02588996763754045</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.06558963125228186</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.5</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.07526881720430108</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.165374677002584</v>
       </c>
-      <c r="U28" t="n">
+      <c r="W28" t="n">
         <v>0.2419462745611356</v>
       </c>
-      <c r="V28" t="n">
+      <c r="X28" t="n">
         <v>0.04383497421472105</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Y28" t="n">
         <v>0.1743589743589744</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.1526889654041646</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>0.05982905982905983</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.1083773768300832</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>0.03490401396160558</v>
       </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
         <v>0.03418803418803418</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.04285714285714285</v>
       </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0.08717948717948719</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3429,104 +3709,114 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>313.14</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>303.57</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>71.3</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>20.4</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>50.06</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  She took a deep breath and tried not to laugh.  The next thing she remembered was looking around and feeling like she could really use a good pedicure session.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.02790597184156044</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.03091766894398466</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.05143201429706136</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
         <v>0.03888635014796693</v>
       </c>
-      <c r="L29" t="n">
+      <c r="N29" t="n">
         <v>0.03123065627456211</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.07940583606383064</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.05644997073886064</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.04527696594185956</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.04540552717835619</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.04283041779820836</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>2.5</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.05835580807002056</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.05193423127939652</v>
       </c>
-      <c r="U29" t="n">
+      <c r="W29" t="n">
         <v>0.04545938683365584</v>
       </c>
-      <c r="V29" t="n">
+      <c r="X29" t="n">
         <v>0.03121966470792453</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Y29" t="n">
         <v>0.08873199155563471</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.04525148290596484</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AA29" t="n">
         <v>0.04494139939022228</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AB29" t="n">
         <v>0.1141626668735103</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AC29" t="n">
         <v>0.1021229754431359</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
         <v>0.1014993513344338</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
         <v>0.1031922925800367</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AF29" t="n">
         <v>0.04403108465608466</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AG29" t="n">
         <v>0.07213321281209212</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.06306231651409316</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -3534,104 +3824,114 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>320.628</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>313.981</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>77.2</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>12.6</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>10.2</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>-15.31</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve">  When she left Hermione's clinic an hour later, she felt worse than she had for ages.  It was like a nightmare.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.001954887218045113</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.0382731643911926</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.002966958867161159</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.001299638989169675</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.00242914979757085</v>
       </c>
-      <c r="M30" t="n">
+      <c r="O30" t="n">
         <v>0.07266921933968887</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.03187691927206777</v>
       </c>
-      <c r="O30" t="n">
+      <c r="Q30" t="n">
         <v>0.06185324736043304</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>0.04474986178706348</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.05196217866183417</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>1</v>
       </c>
-      <c r="S30" t="n">
+      <c r="U30" t="n">
         <v>0.08982027050553851</v>
       </c>
-      <c r="T30" t="n">
+      <c r="V30" t="n">
         <v>0.04988855713024097</v>
       </c>
-      <c r="U30" t="n">
+      <c r="W30" t="n">
         <v>0.03272468272468272</v>
       </c>
-      <c r="V30" t="n">
+      <c r="X30" t="n">
         <v>0.04555547119773767</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Y30" t="n">
         <v>0.02026228563193544</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Z30" t="n">
         <v>0.05876218269919058</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AA30" t="n">
         <v>0.005986887508626639</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AB30" t="n">
         <v>0.07093596059113301</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AC30" t="n">
         <v>0.06139901963806764</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>0.03724137931034483</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AE30" t="n">
         <v>0.04050632911392405</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AF30" t="n">
         <v>0.1031569537262453</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AG30" t="n">
         <v>0.01166666666666667</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AH30" t="n">
         <v>0.03845645248542405</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AI30" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>330.514</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>321.389</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>18.2</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>7.7</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>-52.66999999999999</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  Her face looked pale and she had severe pain in her throat.  As she strolled down the street, she heard a man that sounded exactly like Simon.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.02286480336361508</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>0.008126306417225752</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.02704888836460358</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.01720872780252838</v>
       </c>
-      <c r="L31" t="n">
+      <c r="N31" t="n">
         <v>0.02716938259741012</v>
       </c>
-      <c r="M31" t="n">
+      <c r="O31" t="n">
         <v>0.1233256602986299</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.07459962958776128</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.05509746232116385</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>0.0581616982895219</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.05047764698674509</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>1.8</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>0.03291654173723491</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>0.07188992684828484</v>
       </c>
-      <c r="U31" t="n">
+      <c r="W31" t="n">
         <v>0.01489040060468632</v>
       </c>
-      <c r="V31" t="n">
+      <c r="X31" t="n">
         <v>0.01106460661650118</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.04203995744497561</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.01097541378756227</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AA31" t="n">
         <v>0.001725327812284334</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AB31" t="n">
         <v>0.1081592650660621</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AC31" t="n">
         <v>0.08265958847354196</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AD31" t="n">
         <v>0.0975323995123933</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AE31" t="n">
         <v>0.07289819457060975</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AF31" t="n">
         <v>0.0809835325964358</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AG31" t="n">
         <v>0.07448201515998125</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AH31" t="n">
         <v>0.04950002199547714</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>341.209</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>331.295</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>69.69999999999999</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>25.1</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>5.2</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>-69.08</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve">  And after another second, she realized that she was panicking.  Feeling stressed, she stopped to buy a vodka martini and continued walking home heavy-hearted.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.01769911504424779</v>
       </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>0.01588983050847458</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.01834914182475158</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>0.04259004994299111</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.1072809465719798</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.09103984676985624</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.07426563867227993</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>0.06332467864521979</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.04570927080785848</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>1.6</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.09866365647305649</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.02674897119341564</v>
       </c>
-      <c r="U32" t="n">
+      <c r="W32" t="n">
         <v>0.07202944916123211</v>
       </c>
-      <c r="V32" t="n">
+      <c r="X32" t="n">
         <v>0.04901960784313725</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.09394274141581516</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.0746104135407618</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AA32" t="n">
         <v>0.08574929971988797</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AB32" t="n">
         <v>0.1549991879105803</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>0.125048859643022</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>0.06597701149425288</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>0.1110192115045501</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>0.0740209210358464</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>0.06174242424242424</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.07217151962914674</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>0.8571428571428571</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>349.761</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>342.511</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>83</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>17</v>
       </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
         <v>-64.78</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  As days went by, she noticed that she was thinking about Simon more than ever.  She was completely terrified of meeting Simon.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.04735754675946063</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.02759322033898305</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.06366878735299789</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.02569169960474308</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.0369758064516129</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.03217326521924223</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.03705968688845401</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.0335820895522388</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.06308012558012559</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.05201014832162373</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>0.8</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
         <v>0.07564917859035505</v>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
         <v>0.01373626373626374</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Y33" t="n">
         <v>0.02669902912621359</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.03048780487804878</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>0.01785714285714286</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>0.1491115196078432</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>0.07372881355932204</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.1596631043721836</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>0.1543976920911905</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.1011904761904762</v>
       </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
         <v>0.05603526196578015</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>359.6</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>350.923</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>92.40000000000001</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>7.6</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>34</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">  She called her mom and easily persuaded her to come with her to the finals the next day.  When she arrived at the studios, Simon was staring at his feet.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.05474532063219214</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.005208333333333333</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.05063343018947294</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.02973488755931504</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.01887994634473508</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.0263739793104376</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.03845081784580057</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.03386113589057389</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>0.02792825674914196</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.05205387863264042</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.02439024390243903</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.05161290322580645</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.04933432241812161</v>
       </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>0.06504575261424106</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.02603550295857988</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>0.03660373715298806</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>0.09338699774479592</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.102271846021846</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.04401532567049808</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.1221831341914202</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>0.03261802575107296</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AG34" t="n">
         <v>0.0182741116751269</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AH34" t="n">
         <v>0.0318360914105595</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.7142857142857143</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>368.088</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>360.961</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>73.7</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>9.5</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>16.8</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>42.01</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve">  How are you doing, Simon?  she asked, almost losing control over her voice for a moment.  I am doing great.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.03462394303515798</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.021502319150834</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.03509301156359979</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.02114455592716462</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.04088393421884883</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.07419999326856358</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.06603105030470378</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.0664916244400116</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>0.07347499368459302</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.0491728820042073</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>6</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.0141025641025641</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.02158273381294964</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.1028721030718813</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.0250549220629773</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.03661454631603885</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.1027032395826947</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.009578544061302681</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>0.2202189038618791</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>0.1379485617639568</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.03686868686868687</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>0.08741470394012767</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AF35" t="n">
         <v>0.08661262050832602</v>
       </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
         <v>0.1203475368986708</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>374.795</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>368.489</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>88.5</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>11.5</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
         <v>-29.6</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve">  How are you these days?  Getting by, she answered, actually thinking about the bottle that she was hiding.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.05071757935373176</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.04386446886446887</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.04380440241044526</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0.05864197530864198</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.02542548775425488</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.0516900790166813</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>0.0637530193236715</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.1064654406538735</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.06201550387596899</v>
       </c>
-      <c r="V36" t="n">
+      <c r="X36" t="n">
         <v>0.03065134099616858</v>
       </c>
-      <c r="W36" t="n">
+      <c r="Y36" t="n">
         <v>0.06751054852320675</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.06342997392238074</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="AA36" t="n">
         <v>0.09674502712477395</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="AB36" t="n">
         <v>0.1661567020868006</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.08443543172867807</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AD36" t="n">
         <v>0.115</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AE36" t="n">
         <v>0.1137299771167048</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
         <v>0.09841269841269841</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AG36" t="n">
         <v>0.04597701149425287</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AH36" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -4269,104 +4629,114 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>382.142</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>375.996</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>78</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>13.2</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>8.799999999999999</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>-22.63</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">  I have to go to the dressing room.  Do you need anything?  he inquired impatiently.  No, I'm fine.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.1062223100614325</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.09037586244265433</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.04868913857677902</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.08482097411551312</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.08292599262498927</v>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
       <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
         <v>0.02406417112299465</v>
       </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>0.5</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>0.1241721854304636</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.1249446167478954</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.07459677419354839</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.07023411371237458</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.08928571428571429</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.1449275362318841</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="AA37" t="n">
         <v>0.04320987654320987</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="AB37" t="n">
         <v>0.0958904109589041</v>
       </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
         <v>0.04411764705882353</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AE37" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.05</v>
       </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
         <v>0.05128205128205128</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>389.051</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>382.402</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>92.30000000000001</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>7.7</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>25</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve">  I was just planning to work on the routine, she replied.  By the way, do you have a vodka martini on you by any chance?</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.04085038384237751</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.03973898710740816</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.0301177536231884</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.02997485543925172</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>0.04355607557635639</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.07789083191803425</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.04942263293887526</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.04682636921075858</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.04549003125621426</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.04165135016650737</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>3</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.07532894736842105</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.1696555653548257</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.1533526554562737</v>
       </c>
-      <c r="V38" t="n">
+      <c r="X38" t="n">
         <v>0.1169568990932775</v>
       </c>
-      <c r="W38" t="n">
+      <c r="Y38" t="n">
         <v>0.1233608303319004</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.1754012740394063</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.06840823682797761</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>0.1204044117647059</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>0.03676470588235294</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>0.06818181818181818</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.03289473684210526</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AF38" t="n">
         <v>0.06481481481481481</v>
       </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
         <v>0.02547169811320755</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>396.079</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>389.712</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>70.19999999999999</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>15.2</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>14.6</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>-2.58</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve">  What?  No, he answered, looking at her blamefully.  Rachel felt like a little girl.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.01784273768533483</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.05228996393770791</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.0211002922004945</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.01430776907047049</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.02615796335689288</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.06617008187886968</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.02136986301369863</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.06419748395812226</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.0420166416498829</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.05578758368837492</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.09026275951557093</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.09807498212708693</v>
       </c>
-      <c r="U39" t="n">
+      <c r="W39" t="n">
         <v>0.05511039886039886</v>
       </c>
-      <c r="V39" t="n">
+      <c r="X39" t="n">
         <v>0.02001502933610798</v>
       </c>
-      <c r="W39" t="n">
+      <c r="Y39" t="n">
         <v>0.04204423785025983</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.06527888467382872</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="AA39" t="n">
         <v>0.03056053246270637</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="AB39" t="n">
         <v>0.08469441517386722</v>
       </c>
-      <c r="AA39" t="n">
+      <c r="AC39" t="n">
         <v>0.03608247422680412</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>0.03125</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AE39" t="n">
         <v>0.08995875408903428</v>
       </c>
-      <c r="AD39" t="n">
+      <c r="AF39" t="n">
         <v>0.1059109669811321</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.03461538461538462</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AH39" t="n">
         <v>0.01449275362318841</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4584,104 +4974,114 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>410.334</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>397.08</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>2.9</v>
       </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
         <v>-7.720000000000001</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">  I'm sorry, I'll be back in a jiffy, she said as she ran to find a hidden spot.  On her way to the stage, while licking what was left of her drink, she thought to herself, why didn't I go to a regular psychologist first?</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>milkywayvodka_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.02116755793226382</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.0296108020673058</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.0430913170068349</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.03413461538461539</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.02354166666666667</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.06748472088682828</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.06192531917288017</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.03201258924547546</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.05227332381128895</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.05710425177992801</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>2.5</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>0.09503360048472831</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.04788160852106595</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.05132127683180723</v>
       </c>
-      <c r="V40" t="n">
+      <c r="X40" t="n">
         <v>0.06650251909577715</v>
       </c>
-      <c r="W40" t="n">
+      <c r="Y40" t="n">
         <v>0.04285229119666206</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.0520996513214412</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AA40" t="n">
         <v>0.05035577449370553</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>0.05750514055100571</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>0.06616580734830921</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>0.086217410179095</v>
       </c>
-      <c r="AC40" t="n">
+      <c r="AE40" t="n">
         <v>0.02168462061239644</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.05434574498077555</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.04531326488184847</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>0.06637345120257689</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>1</v>
       </c>
     </row>
